--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/123.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/123.xlsx
@@ -426,13 +426,13 @@
         <v>-8.019690660284098</v>
       </c>
       <c r="E2">
-        <v>-20.25264656799766</v>
+        <v>-26.71863270832378</v>
       </c>
       <c r="F2">
-        <v>-2.842967014064245</v>
+        <v>-2.562833867622522</v>
       </c>
       <c r="G2">
-        <v>-9.3983419875607</v>
+        <v>-14.14023665146395</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.098638752180175</v>
       </c>
       <c r="E3">
-        <v>-21.01480685738461</v>
+        <v>-26.17429654717979</v>
       </c>
       <c r="F3">
-        <v>-2.544777114976298</v>
+        <v>-2.787195521935962</v>
       </c>
       <c r="G3">
-        <v>-8.733296425813128</v>
+        <v>-14.36150854949052</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.183889581566619</v>
       </c>
       <c r="E4">
-        <v>-20.79118175393783</v>
+        <v>-26.1622598632674</v>
       </c>
       <c r="F4">
-        <v>-2.935232232122859</v>
+        <v>-2.592877096587254</v>
       </c>
       <c r="G4">
-        <v>-9.747531709951947</v>
+        <v>-13.93948351468977</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.262086791434863</v>
       </c>
       <c r="E5">
-        <v>-21.29801762182431</v>
+        <v>-26.59399551821067</v>
       </c>
       <c r="F5">
-        <v>-2.667062367712367</v>
+        <v>-2.693764790941609</v>
       </c>
       <c r="G5">
-        <v>-9.341539647197884</v>
+        <v>-14.14984716516445</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.314493148917792</v>
       </c>
       <c r="E6">
-        <v>-21.87778909207833</v>
+        <v>-26.38285088912903</v>
       </c>
       <c r="F6">
-        <v>-2.785634049381685</v>
+        <v>-2.637874013907323</v>
       </c>
       <c r="G6">
-        <v>-9.582616883913152</v>
+        <v>-13.80726694694236</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.333043492164332</v>
       </c>
       <c r="E7">
-        <v>-22.50541747564542</v>
+        <v>-27.33157072220998</v>
       </c>
       <c r="F7">
-        <v>-2.460131220288634</v>
+        <v>-2.626050725967166</v>
       </c>
       <c r="G7">
-        <v>-9.314710986147631</v>
+        <v>-13.76840941867516</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.306468023776766</v>
       </c>
       <c r="E8">
-        <v>-22.17492944256563</v>
+        <v>-27.54247987064322</v>
       </c>
       <c r="F8">
-        <v>-2.392705427170365</v>
+        <v>-2.450172587372178</v>
       </c>
       <c r="G8">
-        <v>-9.168851660232882</v>
+        <v>-13.1769622500839</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.213897271348754</v>
       </c>
       <c r="E9">
-        <v>-23.99323402544349</v>
+        <v>-28.23592509543779</v>
       </c>
       <c r="F9">
-        <v>-2.486037582443785</v>
+        <v>-2.511781584587988</v>
       </c>
       <c r="G9">
-        <v>-9.008886099775298</v>
+        <v>-13.51068675898844</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.04064453413932</v>
       </c>
       <c r="E10">
-        <v>-24.21520623587747</v>
+        <v>-28.54383868558933</v>
       </c>
       <c r="F10">
-        <v>-2.670703042447671</v>
+        <v>-2.618135675433417</v>
       </c>
       <c r="G10">
-        <v>-8.560989151585142</v>
+        <v>-12.86731037306817</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.78137146362444</v>
       </c>
       <c r="E11">
-        <v>-24.75712419190137</v>
+        <v>-29.88764523346948</v>
       </c>
       <c r="F11">
-        <v>-2.458194497300888</v>
+        <v>-2.394250332376586</v>
       </c>
       <c r="G11">
-        <v>-7.973559330005783</v>
+        <v>-12.64497082410518</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.430433671791913</v>
       </c>
       <c r="E12">
-        <v>-25.77631613748968</v>
+        <v>-29.83962982356615</v>
       </c>
       <c r="F12">
-        <v>-2.403766617099947</v>
+        <v>-2.519622910422888</v>
       </c>
       <c r="G12">
-        <v>-8.696923461973157</v>
+        <v>-12.56460071004829</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.988085133402266</v>
       </c>
       <c r="E13">
-        <v>-25.47957429271506</v>
+        <v>-30.3800420619825</v>
       </c>
       <c r="F13">
-        <v>-2.539497929518257</v>
+        <v>-2.559630570875896</v>
       </c>
       <c r="G13">
-        <v>-8.139202476063218</v>
+        <v>-12.31571058586034</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.478475626384618</v>
       </c>
       <c r="E14">
-        <v>-26.61268000196632</v>
+        <v>-30.26778798404337</v>
       </c>
       <c r="F14">
-        <v>-2.443100814854478</v>
+        <v>-2.642550147896126</v>
       </c>
       <c r="G14">
-        <v>-6.993909315115733</v>
+        <v>-12.02313119219063</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.924792776204775</v>
       </c>
       <c r="E15">
-        <v>-27.7906085469455</v>
+        <v>-31.72687815897378</v>
       </c>
       <c r="F15">
-        <v>-2.011026034289062</v>
+        <v>-2.283912622691095</v>
       </c>
       <c r="G15">
-        <v>-6.585103288653291</v>
+        <v>-10.82757070777486</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.350177673008401</v>
       </c>
       <c r="E16">
-        <v>-28.70225829179966</v>
+        <v>-31.29061629425984</v>
       </c>
       <c r="F16">
-        <v>-2.147736476977481</v>
+        <v>-2.312283377869575</v>
       </c>
       <c r="G16">
-        <v>-5.986040210048934</v>
+        <v>-10.65852763144859</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.789733095253434</v>
       </c>
       <c r="E17">
-        <v>-28.55835244478391</v>
+        <v>-32.99104243448103</v>
       </c>
       <c r="F17">
-        <v>-1.6473197289463</v>
+        <v>-2.22900428939653</v>
       </c>
       <c r="G17">
-        <v>-5.487054923096745</v>
+        <v>-10.279298018834</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.269730780877708</v>
       </c>
       <c r="E18">
-        <v>-29.84321637498022</v>
+        <v>-33.11935900972537</v>
       </c>
       <c r="F18">
-        <v>-1.788887718084735</v>
+        <v>-2.318703225241271</v>
       </c>
       <c r="G18">
-        <v>-5.408568509451704</v>
+        <v>-10.11173806690933</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.803650493154049</v>
       </c>
       <c r="E19">
-        <v>-30.84227246089343</v>
+        <v>-34.23860306003916</v>
       </c>
       <c r="F19">
-        <v>-1.519436369302112</v>
+        <v>-2.005077527969559</v>
       </c>
       <c r="G19">
-        <v>-4.40712848382217</v>
+        <v>-9.568845014469783</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.406150646356452</v>
       </c>
       <c r="E20">
-        <v>-31.59546410750819</v>
+        <v>-34.80733863913648</v>
       </c>
       <c r="F20">
-        <v>-1.391437866588935</v>
+        <v>-1.631825116676935</v>
       </c>
       <c r="G20">
-        <v>-4.693993875891096</v>
+        <v>-9.808958882433123</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.084617947699418</v>
       </c>
       <c r="E21">
-        <v>-32.2374522821536</v>
+        <v>-35.10636962752199</v>
       </c>
       <c r="F21">
-        <v>-1.363058827736427</v>
+        <v>-1.831865904044182</v>
       </c>
       <c r="G21">
-        <v>-5.010250291257673</v>
+        <v>-9.313635058847368</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.834212491566842</v>
       </c>
       <c r="E22">
-        <v>-33.28962510393977</v>
+        <v>-35.74413500015524</v>
       </c>
       <c r="F22">
-        <v>-1.331247034366718</v>
+        <v>-1.541145393827279</v>
       </c>
       <c r="G22">
-        <v>-4.538120149720052</v>
+        <v>-9.430831681483108</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.648779657508325</v>
       </c>
       <c r="E23">
-        <v>-32.32988749359816</v>
+        <v>-36.32147920834115</v>
       </c>
       <c r="F23">
-        <v>-1.195147926821565</v>
+        <v>-1.456899600595166</v>
       </c>
       <c r="G23">
-        <v>-4.426150878490822</v>
+        <v>-9.474474603327319</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.526534592488278</v>
       </c>
       <c r="E24">
-        <v>-33.37599442445106</v>
+        <v>-36.49480655098473</v>
       </c>
       <c r="F24">
-        <v>-1.19810271334735</v>
+        <v>-1.177053069274812</v>
       </c>
       <c r="G24">
-        <v>-4.070876373398395</v>
+        <v>-9.568507338824778</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.457493833226672</v>
       </c>
       <c r="E25">
-        <v>-33.50205581963959</v>
+        <v>-36.73421338634824</v>
       </c>
       <c r="F25">
-        <v>-0.8850088279482352</v>
+        <v>-1.034299686382971</v>
       </c>
       <c r="G25">
-        <v>-4.03492384884191</v>
+        <v>-9.717610999368013</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.428928853279412</v>
       </c>
       <c r="E26">
-        <v>-34.54324709195716</v>
+        <v>-37.59221882810753</v>
       </c>
       <c r="F26">
-        <v>-1.098599220923074</v>
+        <v>-1.12105957468258</v>
       </c>
       <c r="G26">
-        <v>-3.667132171065499</v>
+        <v>-9.382491095518668</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.439614656183455</v>
       </c>
       <c r="E27">
-        <v>-34.40364329524871</v>
+        <v>-37.11166622336157</v>
       </c>
       <c r="F27">
-        <v>-0.5654313108874083</v>
+        <v>-1.221006243667354</v>
       </c>
       <c r="G27">
-        <v>-3.813968107914333</v>
+        <v>-9.488471589867357</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.482097626452354</v>
       </c>
       <c r="E28">
-        <v>-33.52212601644158</v>
+        <v>-36.99489725683679</v>
       </c>
       <c r="F28">
-        <v>-0.9691800681140957</v>
+        <v>-0.9411257492834849</v>
       </c>
       <c r="G28">
-        <v>-3.474365725404816</v>
+        <v>-9.75882067024086</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.546854580394074</v>
       </c>
       <c r="E29">
-        <v>-34.11885209338032</v>
+        <v>-37.52665105295047</v>
       </c>
       <c r="F29">
-        <v>-0.6503571937572192</v>
+        <v>-1.261088457186613</v>
       </c>
       <c r="G29">
-        <v>-3.998206588265854</v>
+        <v>-9.66716159589506</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.635870902401011</v>
       </c>
       <c r="E30">
-        <v>-34.02895962009107</v>
+        <v>-36.97398023539536</v>
       </c>
       <c r="F30">
-        <v>-0.7406094790270309</v>
+        <v>-1.024682340836468</v>
       </c>
       <c r="G30">
-        <v>-4.019327868806403</v>
+        <v>-9.564551236905348</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.749273497142831</v>
       </c>
       <c r="E31">
-        <v>-32.93437990346006</v>
+        <v>-36.70466962192219</v>
       </c>
       <c r="F31">
-        <v>-0.9271909528335915</v>
+        <v>-1.070322899628513</v>
       </c>
       <c r="G31">
-        <v>-4.825776762172865</v>
+        <v>-10.18009090065866</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.882283234857659</v>
       </c>
       <c r="E32">
-        <v>-32.85237376765515</v>
+        <v>-36.37773644093843</v>
       </c>
       <c r="F32">
-        <v>-0.7424832460921634</v>
+        <v>-1.124228079998288</v>
       </c>
       <c r="G32">
-        <v>-4.263639508513538</v>
+        <v>-10.12538744616774</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.037518628180409</v>
       </c>
       <c r="E33">
-        <v>-33.0782223518397</v>
+        <v>-36.20941532631033</v>
       </c>
       <c r="F33">
-        <v>-0.9617578961850122</v>
+        <v>-1.153222595831076</v>
       </c>
       <c r="G33">
-        <v>-4.999007678606308</v>
+        <v>-9.966239590458358</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.216870989279109</v>
       </c>
       <c r="E34">
-        <v>-32.69395189720782</v>
+        <v>-35.61624862994162</v>
       </c>
       <c r="F34">
-        <v>-0.5935949742151887</v>
+        <v>-0.9571803379171421</v>
       </c>
       <c r="G34">
-        <v>-5.117862884557223</v>
+        <v>-10.61020690875739</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.416217718217819</v>
       </c>
       <c r="E35">
-        <v>-31.26849017025836</v>
+        <v>-35.75027561090964</v>
       </c>
       <c r="F35">
-        <v>-0.919169871272284</v>
+        <v>-0.9955867641805384</v>
       </c>
       <c r="G35">
-        <v>-5.758085975851338</v>
+        <v>-10.61746693512501</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.632696011688486</v>
       </c>
       <c r="E36">
-        <v>-33.03277232246171</v>
+        <v>-34.72454907732826</v>
       </c>
       <c r="F36">
-        <v>-0.7263168278591283</v>
+        <v>-1.048487134890718</v>
       </c>
       <c r="G36">
-        <v>-5.432536859156027</v>
+        <v>-10.673398602011</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.866629033502267</v>
       </c>
       <c r="E37">
-        <v>-29.93394888019791</v>
+        <v>-35.2183135049916</v>
       </c>
       <c r="F37">
-        <v>-0.5058617542172903</v>
+        <v>-0.8351146025428153</v>
       </c>
       <c r="G37">
-        <v>-5.718789800300189</v>
+        <v>-10.54553540164773</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.11194405222233</v>
       </c>
       <c r="E38">
-        <v>-31.45317266147618</v>
+        <v>-33.87723536270107</v>
       </c>
       <c r="F38">
-        <v>-0.4846795713603041</v>
+        <v>-1.116457993760028</v>
       </c>
       <c r="G38">
-        <v>-5.856674022010834</v>
+        <v>-10.55498700916235</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.358719131210637</v>
       </c>
       <c r="E39">
-        <v>-30.10599240046032</v>
+        <v>-33.25944735315266</v>
       </c>
       <c r="F39">
-        <v>-0.3343366863240134</v>
+        <v>-0.8346258657751636</v>
       </c>
       <c r="G39">
-        <v>-6.0392472979561</v>
+        <v>-10.85240642041047</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.605045203539955</v>
       </c>
       <c r="E40">
-        <v>-30.07803813041097</v>
+        <v>-32.73790979440027</v>
       </c>
       <c r="F40">
-        <v>-0.4612094377367857</v>
+        <v>-0.5460740214187895</v>
       </c>
       <c r="G40">
-        <v>-5.22584625895717</v>
+        <v>-10.52036532391265</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.844776102073228</v>
       </c>
       <c r="E41">
-        <v>-29.14431433900642</v>
+        <v>-32.59633837573548</v>
       </c>
       <c r="F41">
-        <v>-0.1831762026611596</v>
+        <v>-0.8183550732493757</v>
       </c>
       <c r="G41">
-        <v>-5.924848086301045</v>
+        <v>-10.41316323825997</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.066814102955429</v>
       </c>
       <c r="E42">
-        <v>-27.74839864072001</v>
+        <v>-32.36238835155121</v>
       </c>
       <c r="F42">
-        <v>-0.01271641524788296</v>
+        <v>-0.7098588243003077</v>
       </c>
       <c r="G42">
-        <v>-6.010958686323028</v>
+        <v>-10.81954594538766</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.2724043475062</v>
       </c>
       <c r="E43">
-        <v>-27.34066389801739</v>
+        <v>-30.93769872942007</v>
       </c>
       <c r="F43">
-        <v>0.1936083672370011</v>
+        <v>-0.5420730068632679</v>
       </c>
       <c r="G43">
-        <v>-5.408760521092981</v>
+        <v>-11.26324512183402</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.461241893616145</v>
       </c>
       <c r="E44">
-        <v>-27.63152325505605</v>
+        <v>-31.06841313165147</v>
       </c>
       <c r="F44">
-        <v>0.02418072560761262</v>
+        <v>-0.3716306151654499</v>
       </c>
       <c r="G44">
-        <v>-6.334408917146441</v>
+        <v>-10.92090491816353</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.627379950759984</v>
       </c>
       <c r="E45">
-        <v>-26.90866106310765</v>
+        <v>-30.50294711078768</v>
       </c>
       <c r="F45">
-        <v>-0.005578373337959623</v>
+        <v>-0.2613956230379058</v>
       </c>
       <c r="G45">
-        <v>-5.819152298868734</v>
+        <v>-10.73871566550082</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.775451215854716</v>
       </c>
       <c r="E46">
-        <v>-26.2012862522655</v>
+        <v>-29.97668408940829</v>
       </c>
       <c r="F46">
-        <v>0.1445971814829655</v>
+        <v>-0.3641164944546557</v>
       </c>
       <c r="G46">
-        <v>-7.382958005799804</v>
+        <v>-11.18713236934064</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.912453716191299</v>
       </c>
       <c r="E47">
-        <v>-24.47823359166498</v>
+        <v>-28.89447842800325</v>
       </c>
       <c r="F47">
-        <v>0.2875717384713546</v>
+        <v>-0.5935510707428403</v>
       </c>
       <c r="G47">
-        <v>-6.489435143659432</v>
+        <v>-11.17972005787821</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.039434957496951</v>
       </c>
       <c r="E48">
-        <v>-24.23631345322722</v>
+        <v>-28.03919007064855</v>
       </c>
       <c r="F48">
-        <v>0.537244158777334</v>
+        <v>-0.3228770516736851</v>
       </c>
       <c r="G48">
-        <v>-6.115350118812866</v>
+        <v>-11.34124157473925</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.16082568153784</v>
       </c>
       <c r="E49">
-        <v>-23.38990090492756</v>
+        <v>-28.26966675526894</v>
       </c>
       <c r="F49">
-        <v>0.3545220487004163</v>
+        <v>-0.4686647443619812</v>
       </c>
       <c r="G49">
-        <v>-6.735802632146455</v>
+        <v>-10.44896347772165</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.289804753102948</v>
       </c>
       <c r="E50">
-        <v>-22.64977164158792</v>
+        <v>-27.70735708078849</v>
       </c>
       <c r="F50">
-        <v>0.529526259685451</v>
+        <v>-0.213104288556903</v>
       </c>
       <c r="G50">
-        <v>-6.425574720206891</v>
+        <v>-11.0271370139732</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.431751344573344</v>
       </c>
       <c r="E51">
-        <v>-22.56647036221683</v>
+        <v>-26.6444880033962</v>
       </c>
       <c r="F51">
-        <v>0.6275701687459949</v>
+        <v>-0.5020794286561077</v>
       </c>
       <c r="G51">
-        <v>-6.144638515198799</v>
+        <v>-11.34631333050542</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.586059970248295</v>
       </c>
       <c r="E52">
-        <v>-21.89424556662221</v>
+        <v>-27.21217750499775</v>
       </c>
       <c r="F52">
-        <v>0.2513149256182231</v>
+        <v>-0.388594751207381</v>
       </c>
       <c r="G52">
-        <v>-6.221870232084457</v>
+        <v>-11.45127417682801</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.766380553300166</v>
       </c>
       <c r="E53">
-        <v>-20.74879070875203</v>
+        <v>-26.46774166287683</v>
       </c>
       <c r="F53">
-        <v>0.6873352201231736</v>
+        <v>-0.2524128069219479</v>
       </c>
       <c r="G53">
-        <v>-6.593972240152999</v>
+        <v>-11.20102341842342</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.977202670566827</v>
       </c>
       <c r="E54">
-        <v>-20.56182360239734</v>
+        <v>-26.17833594599463</v>
       </c>
       <c r="F54">
-        <v>0.8879972830425202</v>
+        <v>-0.150047305120999</v>
       </c>
       <c r="G54">
-        <v>-6.964008467805035</v>
+        <v>-11.46410585133822</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.210986450804364</v>
       </c>
       <c r="E55">
-        <v>-20.60372104391631</v>
+        <v>-24.49222204787468</v>
       </c>
       <c r="F55">
-        <v>0.625838880874144</v>
+        <v>-0.1925806577851424</v>
       </c>
       <c r="G55">
-        <v>-6.443100748291792</v>
+        <v>-11.79111160807081</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.476196661655938</v>
       </c>
       <c r="E56">
-        <v>-19.00741131384247</v>
+        <v>-25.6226514289874</v>
       </c>
       <c r="F56">
-        <v>0.5151863915755888</v>
+        <v>-0.08302327019308821</v>
       </c>
       <c r="G56">
-        <v>-7.076676264143051</v>
+        <v>-11.36474975861362</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.773373882262185</v>
       </c>
       <c r="E57">
-        <v>-19.47490832802432</v>
+        <v>-24.81276555203361</v>
       </c>
       <c r="F57">
-        <v>0.5679848730952236</v>
+        <v>-0.4078874280185815</v>
       </c>
       <c r="G57">
-        <v>-6.896225047888458</v>
+        <v>-11.84316331558477</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.088157018334305</v>
       </c>
       <c r="E58">
-        <v>-17.66296625112724</v>
+        <v>-24.04950937193681</v>
       </c>
       <c r="F58">
-        <v>0.5516395275031838</v>
+        <v>-0.3831482355339743</v>
       </c>
       <c r="G58">
-        <v>-7.190962917249772</v>
+        <v>-11.64621234036245</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.416178941494431</v>
       </c>
       <c r="E59">
-        <v>-17.99290181037809</v>
+        <v>-23.10301754806763</v>
       </c>
       <c r="F59">
-        <v>0.3743399104449917</v>
+        <v>-0.4366400605697524</v>
       </c>
       <c r="G59">
-        <v>-7.360707829230362</v>
+        <v>-11.1726719064251</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.753277960161336</v>
       </c>
       <c r="E60">
-        <v>-18.34990858724679</v>
+        <v>-23.4295975080788</v>
       </c>
       <c r="F60">
-        <v>0.7702730212262657</v>
+        <v>-0.3323030443501406</v>
       </c>
       <c r="G60">
-        <v>-7.716723896523586</v>
+        <v>-11.61390803699025</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.08318700749899</v>
       </c>
       <c r="E61">
-        <v>-17.67096353622479</v>
+        <v>-23.69116669523584</v>
       </c>
       <c r="F61">
-        <v>0.1397636576876304</v>
+        <v>-0.3442903490360523</v>
       </c>
       <c r="G61">
-        <v>-7.154576711227642</v>
+        <v>-11.94153286573868</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.390639857212562</v>
       </c>
       <c r="E62">
-        <v>-15.72727456502255</v>
+        <v>-23.27600525516064</v>
       </c>
       <c r="F62">
-        <v>0.3893565547229411</v>
+        <v>-0.5225632977925339</v>
       </c>
       <c r="G62">
-        <v>-7.423412872289698</v>
+        <v>-11.84468947707838</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.672088444661849</v>
       </c>
       <c r="E63">
-        <v>-17.581349564087</v>
+        <v>-22.86678970145751</v>
       </c>
       <c r="F63">
-        <v>0.1531028579749109</v>
+        <v>-0.3290889788272786</v>
       </c>
       <c r="G63">
-        <v>-7.686942228852303</v>
+        <v>-11.90791096524184</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.913043131003825</v>
       </c>
       <c r="E64">
-        <v>-16.88405966485992</v>
+        <v>-23.14580709896611</v>
       </c>
       <c r="F64">
-        <v>-0.1327402249743089</v>
+        <v>-0.4478081098942953</v>
       </c>
       <c r="G64">
-        <v>-7.824783413470937</v>
+        <v>-11.84111077735043</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.0934022815921</v>
       </c>
       <c r="E65">
-        <v>-15.71879726168019</v>
+        <v>-22.98468852224721</v>
       </c>
       <c r="F65">
-        <v>-0.4876095068640059</v>
+        <v>-0.4431559985601733</v>
       </c>
       <c r="G65">
-        <v>-7.721881726473771</v>
+        <v>-11.33934132159971</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.2126864518888</v>
       </c>
       <c r="E66">
-        <v>-15.69278117850613</v>
+        <v>-22.98108838541111</v>
       </c>
       <c r="F66">
-        <v>-0.2810345574234764</v>
+        <v>-0.8850071712134295</v>
       </c>
       <c r="G66">
-        <v>-8.103299609689822</v>
+        <v>-12.12901899126422</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.26399037628925</v>
       </c>
       <c r="E67">
-        <v>-16.63422375385675</v>
+        <v>-22.34329810617082</v>
       </c>
       <c r="F67">
-        <v>-0.5114151292856581</v>
+        <v>-0.9774480031614375</v>
       </c>
       <c r="G67">
-        <v>-7.572370868829205</v>
+        <v>-12.31341968834717</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.23348545224723</v>
       </c>
       <c r="E68">
-        <v>-15.22088248758882</v>
+        <v>-22.78908108748589</v>
       </c>
       <c r="F68">
-        <v>-0.5218633273371683</v>
+        <v>-1.182709161901127</v>
       </c>
       <c r="G68">
-        <v>-7.768590213487347</v>
+        <v>-11.18595381512866</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.12798464320977</v>
       </c>
       <c r="E69">
-        <v>-15.3777941119546</v>
+        <v>-22.47836437192359</v>
       </c>
       <c r="F69">
-        <v>-0.8273378893653336</v>
+        <v>-0.8472319609109665</v>
       </c>
       <c r="G69">
-        <v>-7.426008339992487</v>
+        <v>-11.74404889268454</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.953538297042346</v>
       </c>
       <c r="E70">
-        <v>-16.91112182552976</v>
+        <v>-21.81355721675354</v>
       </c>
       <c r="F70">
-        <v>-1.144357407886316</v>
+        <v>-1.370316154552353</v>
       </c>
       <c r="G70">
-        <v>-7.404516278351538</v>
+        <v>-11.36536552008392</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.709374572206402</v>
       </c>
       <c r="E71">
-        <v>-15.3782062030893</v>
+        <v>-21.67105972515417</v>
       </c>
       <c r="F71">
-        <v>-0.9357968617812756</v>
+        <v>-1.381477576937674</v>
       </c>
       <c r="G71">
-        <v>-6.958903606583479</v>
+        <v>-11.28020173608617</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.406552448094663</v>
       </c>
       <c r="E72">
-        <v>-15.4723712916048</v>
+        <v>-22.31955078847459</v>
       </c>
       <c r="F72">
-        <v>-1.334843805629673</v>
+        <v>-0.9950259594488431</v>
       </c>
       <c r="G72">
-        <v>-7.387096187723893</v>
+        <v>-11.13118414972696</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.063126083748326</v>
       </c>
       <c r="E73">
-        <v>-15.16342068090549</v>
+        <v>-21.90201189954536</v>
       </c>
       <c r="F73">
-        <v>-1.451536750029442</v>
+        <v>-1.463443703077282</v>
       </c>
       <c r="G73">
-        <v>-6.962783565955505</v>
+        <v>-11.73386565460574</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.688921237101651</v>
       </c>
       <c r="E74">
-        <v>-15.09359161170722</v>
+        <v>-22.41259281543619</v>
       </c>
       <c r="F74">
-        <v>-1.885391692143475</v>
+        <v>-1.650360665681977</v>
       </c>
       <c r="G74">
-        <v>-6.747654385177046</v>
+        <v>-11.150239649851</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.294768261512091</v>
       </c>
       <c r="E75">
-        <v>-15.57835569728031</v>
+        <v>-22.37219882728777</v>
       </c>
       <c r="F75">
-        <v>-1.499062673030258</v>
+        <v>-1.642769506802722</v>
       </c>
       <c r="G75">
-        <v>-6.415699362863245</v>
+        <v>-10.55394418731747</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.907004009778722</v>
       </c>
       <c r="E76">
-        <v>-16.23090880178561</v>
+        <v>-22.52710433766815</v>
       </c>
       <c r="F76">
-        <v>-1.633331916982627</v>
+        <v>-1.793459477780786</v>
       </c>
       <c r="G76">
-        <v>-6.049298114213328</v>
+        <v>-10.47947677595711</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.539053908897974</v>
       </c>
       <c r="E77">
-        <v>-16.30509426297927</v>
+        <v>-22.13515132688226</v>
       </c>
       <c r="F77">
-        <v>-1.604551948307164</v>
+        <v>-2.026769156779267</v>
       </c>
       <c r="G77">
-        <v>-5.791668149801705</v>
+        <v>-10.95881066458818</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.196563933024434</v>
       </c>
       <c r="E78">
-        <v>-15.11237572189103</v>
+        <v>-22.54918517692955</v>
       </c>
       <c r="F78">
-        <v>-1.960599997011045</v>
+        <v>-1.864548311554234</v>
       </c>
       <c r="G78">
-        <v>-6.09689382743143</v>
+        <v>-10.13436564567025</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.903022317910581</v>
       </c>
       <c r="E79">
-        <v>-16.71264786672159</v>
+        <v>-23.43352822351746</v>
       </c>
       <c r="F79">
-        <v>-1.916481149137943</v>
+        <v>-2.024448899684025</v>
       </c>
       <c r="G79">
-        <v>-5.712271336133364</v>
+        <v>-10.56764653530452</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.669446629906502</v>
       </c>
       <c r="E80">
-        <v>-17.76276476130828</v>
+        <v>-23.64375810084954</v>
       </c>
       <c r="F80">
-        <v>-1.953796615531852</v>
+        <v>-1.841798857571151</v>
       </c>
       <c r="G80">
-        <v>-5.826925459794943</v>
+        <v>-10.05455170326396</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.491923369897628</v>
       </c>
       <c r="E81">
-        <v>-18.10925642153117</v>
+        <v>-23.97778740060332</v>
       </c>
       <c r="F81">
-        <v>-2.114175171653059</v>
+        <v>-2.124309418458908</v>
       </c>
       <c r="G81">
-        <v>-5.112360757870953</v>
+        <v>-10.11440305606844</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.382641701061575</v>
       </c>
       <c r="E82">
-        <v>-17.86004543994105</v>
+        <v>-23.76447816094602</v>
       </c>
       <c r="F82">
-        <v>-2.059458191228541</v>
+        <v>-2.32420358479586</v>
       </c>
       <c r="G82">
-        <v>-5.551527797474051</v>
+        <v>-10.35593383752259</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.346449863770109</v>
       </c>
       <c r="E83">
-        <v>-18.929793269351</v>
+        <v>-24.60825513737321</v>
       </c>
       <c r="F83">
-        <v>-2.290952088880085</v>
+        <v>-2.082424677471157</v>
       </c>
       <c r="G83">
-        <v>-5.047623039850506</v>
+        <v>-10.10797397663118</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.37330663212753</v>
       </c>
       <c r="E84">
-        <v>-19.97662702028213</v>
+        <v>-25.30896856295009</v>
       </c>
       <c r="F84">
-        <v>-2.492387846953646</v>
+        <v>-2.241599615756096</v>
       </c>
       <c r="G84">
-        <v>-4.524040399541532</v>
+        <v>-9.803330955016362</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.461154710624409</v>
       </c>
       <c r="E85">
-        <v>-20.13169555572679</v>
+        <v>-25.49682777868428</v>
       </c>
       <c r="F85">
-        <v>-2.317610608636979</v>
+        <v>-2.264010267471434</v>
       </c>
       <c r="G85">
-        <v>-4.827137396389505</v>
+        <v>-9.823180986069831</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.612490480091738</v>
       </c>
       <c r="E86">
-        <v>-21.01596614673057</v>
+        <v>-27.18334923946492</v>
       </c>
       <c r="F86">
-        <v>-2.44749530392633</v>
+        <v>-2.453090097364838</v>
       </c>
       <c r="G86">
-        <v>-4.819562868195653</v>
+        <v>-10.11361845677563</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.817398077924145</v>
       </c>
       <c r="E87">
-        <v>-22.76030263516714</v>
+        <v>-27.70214933567967</v>
       </c>
       <c r="F87">
-        <v>-2.545691632588989</v>
+        <v>-2.478871376042167</v>
       </c>
       <c r="G87">
-        <v>-4.214630192350168</v>
+        <v>-9.553861485359041</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.065153736828017</v>
       </c>
       <c r="E88">
-        <v>-23.62763673338224</v>
+        <v>-28.49600441464631</v>
       </c>
       <c r="F88">
-        <v>-2.620200795368596</v>
+        <v>-2.389954419025668</v>
       </c>
       <c r="G88">
-        <v>-4.68057954536597</v>
+        <v>-9.615765376397874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.362072241308226</v>
       </c>
       <c r="E89">
-        <v>-23.82094370334766</v>
+        <v>-29.56465182487239</v>
       </c>
       <c r="F89">
-        <v>-2.603020455434534</v>
+        <v>-2.655546404078648</v>
       </c>
       <c r="G89">
-        <v>-4.170338403580259</v>
+        <v>-9.881145327916931</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.702601037619186</v>
       </c>
       <c r="E90">
-        <v>-25.98059559997569</v>
+        <v>-30.62315318908428</v>
       </c>
       <c r="F90">
-        <v>-2.345746935840467</v>
+        <v>-2.810288748391207</v>
       </c>
       <c r="G90">
-        <v>-4.109579961298015</v>
+        <v>-10.37351945542719</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.072389324999875</v>
       </c>
       <c r="E91">
-        <v>-27.92623634347523</v>
+        <v>-31.90070363375821</v>
       </c>
       <c r="F91">
-        <v>-2.703860104479527</v>
+        <v>-2.617685043566294</v>
       </c>
       <c r="G91">
-        <v>-4.157046563240085</v>
+        <v>-9.782941305039991</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.47707422431237</v>
       </c>
       <c r="E92">
-        <v>-29.19723861473406</v>
+        <v>-33.64633300152396</v>
       </c>
       <c r="F92">
-        <v>-2.747093427599035</v>
+        <v>-3.129765204628892</v>
       </c>
       <c r="G92">
-        <v>-4.375946455387774</v>
+        <v>-10.15822805791731</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.911635704844183</v>
       </c>
       <c r="E93">
-        <v>-30.63718693003405</v>
+        <v>-34.2615918583391</v>
       </c>
       <c r="F93">
-        <v>-2.595659582693258</v>
+        <v>-2.962570841517451</v>
       </c>
       <c r="G93">
-        <v>-5.753457833187436</v>
+        <v>-10.77724048394132</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.353961917015013</v>
       </c>
       <c r="E94">
-        <v>-32.16140561814279</v>
+        <v>-35.63249905891815</v>
       </c>
       <c r="F94">
-        <v>-2.52782871791502</v>
+        <v>-3.021321971193603</v>
       </c>
       <c r="G94">
-        <v>-5.41571928781653</v>
+        <v>-10.23074555795505</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.80225357747387</v>
       </c>
       <c r="E95">
-        <v>-33.81203892241264</v>
+        <v>-37.03139902157561</v>
       </c>
       <c r="F95">
-        <v>-3.007862657632917</v>
+        <v>-3.081577416073239</v>
       </c>
       <c r="G95">
-        <v>-5.32795672557045</v>
+        <v>-10.09738354145105</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.24751933901975</v>
       </c>
       <c r="E96">
-        <v>-35.82900313153299</v>
+        <v>-39.67070462085908</v>
       </c>
       <c r="F96">
-        <v>-3.015189567310679</v>
+        <v>-3.406762980451019</v>
       </c>
       <c r="G96">
-        <v>-5.527082729212073</v>
+        <v>-10.10083644044851</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.66787954032878</v>
       </c>
       <c r="E97">
-        <v>-37.13437425627303</v>
+        <v>-41.13391117866247</v>
       </c>
       <c r="F97">
-        <v>-3.13164062842883</v>
+        <v>-3.366858865923361</v>
       </c>
       <c r="G97">
-        <v>-6.381292863073599</v>
+        <v>-10.83142087223703</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.04882884873229</v>
       </c>
       <c r="E98">
-        <v>-38.8945921030545</v>
+        <v>-42.36440398568569</v>
       </c>
       <c r="F98">
-        <v>-3.112627939799776</v>
+        <v>-3.431761451932702</v>
       </c>
       <c r="G98">
-        <v>-6.025131131776648</v>
+        <v>-10.89864812050301</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.38417747558263</v>
       </c>
       <c r="E99">
-        <v>-42.59204584557727</v>
+        <v>-43.91503952691816</v>
       </c>
       <c r="F99">
-        <v>-3.141832032585473</v>
+        <v>-3.731577436232344</v>
       </c>
       <c r="G99">
-        <v>-6.268058963448368</v>
+        <v>-11.2924275807627</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.65299330806181</v>
       </c>
       <c r="E100">
-        <v>-43.42093999217825</v>
+        <v>-46.45793617881534</v>
       </c>
       <c r="F100">
-        <v>-3.350966637300653</v>
+        <v>-3.588971502738201</v>
       </c>
       <c r="G100">
-        <v>-6.086680794442779</v>
+        <v>-11.7823519045739</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.83774660590056</v>
       </c>
       <c r="E101">
-        <v>-46.06765643917528</v>
+        <v>-48.29924314541515</v>
       </c>
       <c r="F101">
-        <v>-3.137777174148769</v>
+        <v>-4.020024906295966</v>
       </c>
       <c r="G101">
-        <v>-7.425922265808466</v>
+        <v>-12.24831449977186</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.93445350003013</v>
       </c>
       <c r="E102">
-        <v>-48.11420969746175</v>
+        <v>-49.60441048882485</v>
       </c>
       <c r="F102">
-        <v>-3.394841116789928</v>
+        <v>-4.042950802535845</v>
       </c>
       <c r="G102">
-        <v>-7.614305549175153</v>
+        <v>-12.00494636554342</v>
       </c>
     </row>
   </sheetData>
